--- a/01_DESIGN/Requirements.xlsx
+++ b/01_DESIGN/Requirements.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TAN DAT\HCMUT\HK 252\Embedded System\Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95654E2E-5609-4405-B959-4E3BDBCD7239}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{741FF487-D4B3-4346-B2D2-F506FF475A9B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9648" activeTab="1" xr2:uid="{49F7B194-0C1C-4F63-AE81-4963B1F93682}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9648" xr2:uid="{49F7B194-0C1C-4F63-AE81-4963B1F93682}"/>
   </bookViews>
   <sheets>
     <sheet name="Functional_Requirements" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="150">
   <si>
     <t>ID</t>
   </si>
@@ -470,13 +470,19 @@
   </si>
   <si>
     <t>PCB/layout constraints (If possible)</t>
+  </si>
+  <si>
+    <t>Digtal Clock with LCD Display</t>
+  </si>
+  <si>
+    <t>s</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -498,6 +504,12 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="28"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="5">
@@ -523,7 +535,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -546,11 +558,91 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thick">
+        <color theme="4" tint="-0.24994659260841701"/>
+      </left>
+      <right/>
+      <top style="thick">
+        <color theme="4" tint="-0.24994659260841701"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thick">
+        <color theme="4" tint="-0.24994659260841701"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thick">
+        <color theme="4" tint="-0.24994659260841701"/>
+      </right>
+      <top style="thick">
+        <color theme="4" tint="-0.24994659260841701"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color theme="4" tint="-0.24994659260841701"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thick">
+        <color theme="4" tint="-0.24994659260841701"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color theme="4" tint="-0.24994659260841701"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4" tint="-0.24994659260841701"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4" tint="-0.24994659260841701"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thick">
+        <color theme="4" tint="-0.24994659260841701"/>
+      </right>
+      <top/>
+      <bottom style="thick">
+        <color theme="4" tint="-0.24994659260841701"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -581,6 +673,33 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -896,14 +1015,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9714532-8226-4F0A-A942-A71DF1255763}">
-  <dimension ref="A1:B41"/>
+  <dimension ref="A1:N41"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.77734375" customWidth="1"/>
     <col min="2" max="2" width="105.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -911,7 +1030,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
@@ -919,7 +1038,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>4</v>
       </c>
@@ -927,7 +1046,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>96</v>
       </c>
@@ -935,7 +1054,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>97</v>
       </c>
@@ -943,7 +1062,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>99</v>
       </c>
@@ -951,7 +1070,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>100</v>
       </c>
@@ -959,7 +1078,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>101</v>
       </c>
@@ -967,7 +1086,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>102</v>
       </c>
@@ -975,7 +1094,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>6</v>
       </c>
@@ -983,7 +1102,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>7</v>
       </c>
@@ -991,7 +1110,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" ht="28.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
         <v>11</v>
       </c>
@@ -999,31 +1118,57 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="47.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" ht="47.4" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>12</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="14" spans="1:2" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E13" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="F13" s="12"/>
+      <c r="G13" s="12"/>
+      <c r="H13" s="12"/>
+      <c r="I13" s="12"/>
+      <c r="J13" s="12"/>
+      <c r="K13" s="12"/>
+      <c r="L13" s="13"/>
+    </row>
+    <row r="14" spans="1:12" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
         <v>103</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="15" spans="1:2" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E14" s="14"/>
+      <c r="F14" s="15"/>
+      <c r="G14" s="15"/>
+      <c r="H14" s="15"/>
+      <c r="I14" s="15"/>
+      <c r="J14" s="15"/>
+      <c r="K14" s="15"/>
+      <c r="L14" s="16"/>
+    </row>
+    <row r="15" spans="1:12" ht="28.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
         <v>104</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="16" spans="1:2" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E15" s="17"/>
+      <c r="F15" s="18"/>
+      <c r="G15" s="18"/>
+      <c r="H15" s="18"/>
+      <c r="I15" s="18"/>
+      <c r="J15" s="18"/>
+      <c r="K15" s="18"/>
+      <c r="L15" s="19"/>
+    </row>
+    <row r="16" spans="1:12" ht="28.05" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
         <v>105</v>
       </c>
@@ -1031,15 +1176,18 @@
         <v>18</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:14" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
         <v>106</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="N17" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
         <v>107</v>
       </c>
@@ -1047,7 +1195,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
         <v>108</v>
       </c>
@@ -1055,7 +1203,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
         <v>109</v>
       </c>
@@ -1063,7 +1211,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
         <v>110</v>
       </c>
@@ -1071,7 +1219,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>14</v>
       </c>
@@ -1079,7 +1227,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
         <v>16</v>
       </c>
@@ -1087,7 +1235,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>19</v>
       </c>
@@ -1095,7 +1243,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
         <v>21</v>
       </c>
@@ -1103,7 +1251,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="26" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
         <v>118</v>
       </c>
@@ -1111,7 +1259,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
         <v>119</v>
       </c>
@@ -1119,7 +1267,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
         <v>120</v>
       </c>
@@ -1127,7 +1275,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
         <v>22</v>
       </c>
@@ -1135,7 +1283,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="30" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
         <v>24</v>
       </c>
@@ -1143,7 +1291,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
         <v>28</v>
       </c>
@@ -1151,7 +1299,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="32" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
         <v>30</v>
       </c>
@@ -1232,20 +1380,24 @@
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="E13:L15"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37D201F4-42B5-4B42-921E-920D09B92191}">
-  <dimension ref="A1:B34"/>
+  <dimension ref="A1:L34"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.77734375" customWidth="1"/>
     <col min="2" max="2" width="105.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1253,7 +1405,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>47</v>
       </c>
@@ -1261,7 +1413,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>48</v>
       </c>
@@ -1269,7 +1421,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>50</v>
       </c>
@@ -1277,7 +1429,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>52</v>
       </c>
@@ -1285,7 +1437,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>54</v>
       </c>
@@ -1293,7 +1445,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>55</v>
       </c>
@@ -1301,7 +1453,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>56</v>
       </c>
@@ -1309,7 +1461,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>58</v>
       </c>
@@ -1317,7 +1469,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>60</v>
       </c>
@@ -1325,7 +1477,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>61</v>
       </c>
@@ -1333,7 +1485,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>63</v>
       </c>
@@ -1341,7 +1493,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
         <v>65</v>
       </c>
@@ -1349,31 +1501,57 @@
         <v>66</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
         <v>67</v>
       </c>
       <c r="B14" s="10" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E14" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="F14" s="12"/>
+      <c r="G14" s="12"/>
+      <c r="H14" s="12"/>
+      <c r="I14" s="12"/>
+      <c r="J14" s="12"/>
+      <c r="K14" s="12"/>
+      <c r="L14" s="13"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>69</v>
       </c>
       <c r="B15" s="9" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E15" s="14"/>
+      <c r="F15" s="15"/>
+      <c r="G15" s="15"/>
+      <c r="H15" s="15"/>
+      <c r="I15" s="15"/>
+      <c r="J15" s="15"/>
+      <c r="K15" s="15"/>
+      <c r="L15" s="16"/>
+    </row>
+    <row r="16" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="4" t="s">
         <v>71</v>
       </c>
       <c r="B16" s="10" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E16" s="17"/>
+      <c r="F16" s="18"/>
+      <c r="G16" s="18"/>
+      <c r="H16" s="18"/>
+      <c r="I16" s="18"/>
+      <c r="J16" s="18"/>
+      <c r="K16" s="18"/>
+      <c r="L16" s="19"/>
+    </row>
+    <row r="17" spans="1:2" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>72</v>
       </c>
@@ -1518,6 +1696,9 @@
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="E14:L16"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>